--- a/data/demo_variants/дефицит/Структура цены Грант-26.xlsx
+++ b/data/demo_variants/дефицит/Структура цены Грант-26.xlsx
@@ -1529,7 +1529,7 @@
         <v/>
       </c>
       <c r="D7" s="130" t="n">
-        <v>1445532</v>
+        <v>1695511</v>
       </c>
       <c r="E7" s="130">
         <f>SUM(E8:E9)</f>
@@ -1570,13 +1570,13 @@
         <v/>
       </c>
       <c r="D8" s="129" t="n">
-        <v>1330000</v>
+        <v>1560000</v>
       </c>
       <c r="E8" s="129" t="n">
-        <v>760000</v>
+        <v>780000</v>
       </c>
       <c r="F8" s="129" t="n">
-        <v>570000</v>
+        <v>780000</v>
       </c>
       <c r="G8" s="129">
         <f>'Расшифровка ФОТ'!I38</f>
@@ -1609,13 +1609,13 @@
         <v/>
       </c>
       <c r="D9" s="130" t="n">
-        <v>115532</v>
+        <v>135511</v>
       </c>
       <c r="E9" s="130" t="n">
-        <v>66018</v>
+        <v>67755</v>
       </c>
       <c r="F9" s="130" t="n">
-        <v>49514</v>
+        <v>67755</v>
       </c>
       <c r="G9" s="130">
         <f>G8*0.086866</f>
@@ -1648,7 +1648,7 @@
         <v/>
       </c>
       <c r="D10" s="130" t="n">
-        <v>436551</v>
+        <v>512044</v>
       </c>
       <c r="E10" s="130">
         <f>E7*0.302</f>
@@ -3379,12 +3379,12 @@
       </c>
       <c r="J7" s="178" t="inlineStr">
         <is>
-          <t>01.06.2026</t>
+          <t>01.05.2026</t>
         </is>
       </c>
       <c r="K7" s="179" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="N7" s="88" t="n"/>
@@ -3422,19 +3422,19 @@
         <v>4</v>
       </c>
       <c r="H8" s="127" t="n">
-        <v>90000</v>
+        <v>95000</v>
       </c>
       <c r="I8" s="57" t="n">
-        <v>360000</v>
+        <v>380000</v>
       </c>
       <c r="J8" s="178" t="inlineStr">
         <is>
-          <t>01.06.2026</t>
+          <t>01.05.2026</t>
         </is>
       </c>
       <c r="K8" s="179" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="N8" s="88" t="n"/>
@@ -3466,20 +3466,20 @@
         <v>1</v>
       </c>
       <c r="F9" s="190" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9" s="191" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H9" s="127" t="n">
         <v>100000</v>
       </c>
       <c r="I9" s="57" t="n">
-        <v>300000</v>
+        <v>400000</v>
       </c>
       <c r="J9" s="178" t="inlineStr">
         <is>
-          <t>01.10.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="K9" s="179" t="inlineStr">
@@ -3516,20 +3516,20 @@
         <v>1</v>
       </c>
       <c r="F10" s="190" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" s="191" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H10" s="127" t="n">
-        <v>90000</v>
+        <v>95000</v>
       </c>
       <c r="I10" s="57" t="n">
-        <v>270000</v>
+        <v>380000</v>
       </c>
       <c r="J10" s="178" t="inlineStr">
         <is>
-          <t>01.10.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="K10" s="179" t="inlineStr">
@@ -3550,11 +3550,11 @@
       <c r="E11" s="125" t="n"/>
       <c r="F11" s="190" t="n"/>
       <c r="G11" s="191" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H11" s="127" t="n"/>
       <c r="I11" s="57" t="n">
-        <v>1330000</v>
+        <v>1560000</v>
       </c>
       <c r="J11" s="178" t="n"/>
       <c r="K11" s="179" t="n"/>
